--- a/data/trans_dic/P36$fruta-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P36$fruta-Edad-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que desayuna, al menos, fruta o zumo</t>
+          <t>Población que desayuna, al menos, fruta o zumo (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,02; 11,27</t>
+          <t>5,91; 10,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13,88; 20,87</t>
+          <t>14,28; 21,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16,03; 24,02</t>
+          <t>15,66; 23,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12,54; 19,09</t>
+          <t>12,61; 19,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,15; 18,01</t>
+          <t>11,11; 17,84</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,51; 18,19</t>
+          <t>11,37; 18,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,73; 13,83</t>
+          <t>9,79; 13,96</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,47; 18,45</t>
+          <t>13,55; 18,48</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,07; 20,09</t>
+          <t>14,76; 19,8</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,39; 14,43</t>
+          <t>9,27; 14,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,75; 17,18</t>
+          <t>12,01; 17,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,12; 20,73</t>
+          <t>14,19; 20,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,36; 14,5</t>
+          <t>9,29; 14,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,41; 18,53</t>
+          <t>12,5; 18,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,65; 19,63</t>
+          <t>13,4; 19,24</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,02; 13,59</t>
+          <t>9,99; 13,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,98; 17,07</t>
+          <t>13,05; 17,07</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14,74; 18,98</t>
+          <t>14,58; 18,81</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,63; 10,22</t>
+          <t>5,76; 10,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,58; 13,26</t>
+          <t>8,44; 13,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,37; 11,8</t>
+          <t>7,19; 11,79</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,24; 13,0</t>
+          <t>8,29; 12,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,7; 13,43</t>
+          <t>8,63; 13,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,77; 18,43</t>
+          <t>12,73; 18,57</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,64; 10,97</t>
+          <t>7,59; 11,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,11; 12,47</t>
+          <t>9,11; 12,5</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10,63; 14,37</t>
+          <t>10,65; 14,41</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,9; 8,05</t>
+          <t>3,79; 8,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,54; 11,54</t>
+          <t>6,41; 11,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,83; 14,18</t>
+          <t>8,78; 13,91</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,78; 12,2</t>
+          <t>6,87; 11,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,48; 13,3</t>
+          <t>7,53; 12,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,18; 15,35</t>
+          <t>9,91; 15,34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,02; 9,58</t>
+          <t>6,09; 9,37</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,64; 11,31</t>
+          <t>7,65; 11,31</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,96; 13,91</t>
+          <t>10,15; 13,78</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,77; 9,02</t>
+          <t>3,56; 8,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,03; 15,04</t>
+          <t>8,21; 14,75</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,51; 17,55</t>
+          <t>10,76; 17,61</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,27; 11,8</t>
+          <t>6,6; 12,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,98; 16,57</t>
+          <t>9,84; 16,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,08; 15,09</t>
+          <t>9,03; 15,04</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,77; 9,53</t>
+          <t>5,81; 9,44</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,94; 14,77</t>
+          <t>9,75; 14,51</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10,71; 15,06</t>
+          <t>10,6; 15,13</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,98; 11,44</t>
+          <t>4,86; 11,49</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,64; 13,98</t>
+          <t>6,99; 14,29</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,81; 12,19</t>
+          <t>5,87; 11,98</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,85; 14,11</t>
+          <t>7,82; 14,57</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9,72; 17,28</t>
+          <t>9,79; 17,05</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,99; 17,08</t>
+          <t>10,04; 17,3</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,02; 11,64</t>
+          <t>7,26; 12,01</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9,43; 14,82</t>
+          <t>9,41; 14,67</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8,97; 13,43</t>
+          <t>8,84; 13,78</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,21; 11,84</t>
+          <t>4,13; 11,35</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,82; 16,13</t>
+          <t>7,3; 16,03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,55; 15,05</t>
+          <t>7,24; 14,26</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,78; 9,21</t>
+          <t>3,78; 9,19</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>9,61; 16,91</t>
+          <t>9,57; 16,54</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,88; 11,09</t>
+          <t>5,06; 10,99</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,38; 8,73</t>
+          <t>4,42; 9,02</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9,56; 15,09</t>
+          <t>9,56; 15,43</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,49; 11,32</t>
+          <t>6,32; 11,07</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,17; 9,19</t>
+          <t>7,11; 9,18</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10,97; 13,25</t>
+          <t>10,89; 13,2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11,9; 14,16</t>
+          <t>11,88; 14,31</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9,66; 11,82</t>
+          <t>9,54; 11,64</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>11,53; 13,74</t>
+          <t>11,57; 13,81</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,31; 14,69</t>
+          <t>12,17; 14,47</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,72; 10,18</t>
+          <t>8,63; 10,11</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>11,46; 13,09</t>
+          <t>11,44; 13,12</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>12,34; 14,01</t>
+          <t>12,34; 13,99</t>
         </is>
       </c>
     </row>
@@ -1543,7 +1543,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que desayuna, al menos, fruta o zumo</t>
+          <t>Población que desayuna, al menos, fruta o zumo (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1750,47 +1750,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>29685; 55592</t>
+          <t>29162; 53147</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>63026; 94793</t>
+          <t>64871; 96045</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>67239; 100757</t>
+          <t>65700; 99945</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>58609; 89228</t>
+          <t>58960; 90640</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>47728; 77114</t>
+          <t>47557; 76418</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>45426; 71822</t>
+          <t>44874; 72463</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>93518; 132838</t>
+          <t>94067; 134116</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>118878; 162776</t>
+          <t>119544; 163093</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>122737; 163592</t>
+          <t>120186; 161239</t>
         </is>
       </c>
     </row>
@@ -1913,47 +1913,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>69065; 106130</t>
+          <t>68172; 108069</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>80634; 117911</t>
+          <t>82438; 118208</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>83383; 122431</t>
+          <t>83773; 120765</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>58368; 90409</t>
+          <t>57896; 90870</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>75569; 112867</t>
+          <t>76164; 113730</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>76909; 110620</t>
+          <t>75512; 108406</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>136166; 184713</t>
+          <t>135796; 186021</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>168104; 221156</t>
+          <t>169048; 221152</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>170074; 219088</t>
+          <t>168211; 217089</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>35753; 64862</t>
+          <t>36538; 64331</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>58261; 90071</t>
+          <t>57280; 91498</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>49294; 78933</t>
+          <t>48126; 78853</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>56826; 89655</t>
+          <t>57198; 89200</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>61645; 95209</t>
+          <t>61194; 93403</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>84449; 121924</t>
+          <t>84175; 122835</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>101254; 145303</t>
+          <t>100576; 147080</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>126470; 173077</t>
+          <t>126468; 173503</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>141403; 191231</t>
+          <t>141644; 191733</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20166; 41641</t>
+          <t>19614; 41629</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>40117; 70798</t>
+          <t>39308; 71106</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>56823; 91270</t>
+          <t>56523; 89578</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>34807; 62655</t>
+          <t>35300; 61579</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>46079; 81943</t>
+          <t>46372; 78860</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>65970; 99459</t>
+          <t>64242; 99422</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>62110; 98714</t>
+          <t>62820; 96561</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>93894; 139062</t>
+          <t>94020; 139109</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>128675; 179629</t>
+          <t>131112; 177986</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>14560; 34872</t>
+          <t>13766; 32857</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>34481; 64596</t>
+          <t>35264; 63361</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>50218; 83891</t>
+          <t>51429; 84158</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>25317; 47690</t>
+          <t>26660; 49199</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>44588; 74042</t>
+          <t>43957; 74793</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>45094; 74959</t>
+          <t>44874; 74715</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>45597; 75370</t>
+          <t>45935; 74640</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>87112; 129417</t>
+          <t>85453; 127163</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>104352; 146810</t>
+          <t>103330; 147464</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>14563; 33457</t>
+          <t>14214; 33630</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>20573; 43307</t>
+          <t>21668; 44264</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>19413; 40741</t>
+          <t>19630; 40056</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>26934; 48381</t>
+          <t>26833; 49949</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>34424; 61171</t>
+          <t>34661; 60360</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>37724; 64506</t>
+          <t>37931; 65338</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>44595; 73945</t>
+          <t>46122; 76331</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>62565; 98369</t>
+          <t>62461; 97359</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>63856; 95661</t>
+          <t>62917; 98137</t>
         </is>
       </c>
     </row>
@@ -2728,47 +2728,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>8840; 24854</t>
+          <t>8666; 23829</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>16972; 40129</t>
+          <t>18158; 39871</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>19278; 38410</t>
+          <t>18465; 36398</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>12613; 30740</t>
+          <t>12612; 30688</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>37377; 65777</t>
+          <t>37229; 64327</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19462; 44241</t>
+          <t>20202; 43839</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23793; 47447</t>
+          <t>24010; 49064</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>60971; 96211</t>
+          <t>60989; 98435</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>42467; 74073</t>
+          <t>41365; 72429</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>234573; 300452</t>
+          <t>232577; 300228</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>375159; 453293</t>
+          <t>372498; 451700</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>403547; 479964</t>
+          <t>402872; 485161</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>326152; 398925</t>
+          <t>321891; 392999</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>409578; 488101</t>
+          <t>411155; 490463</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>435813; 520047</t>
+          <t>431133; 512593</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>579619; 676510</t>
+          <t>573255; 671909</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>798805; 912944</t>
+          <t>797553; 915117</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>855413; 971375</t>
+          <t>855408; 969735</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P36$fruta-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P36$fruta-Edad-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,91; 10,78</t>
+          <t>6,0; 11,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14,28; 21,15</t>
+          <t>13,88; 20,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15,66; 23,83</t>
+          <t>16,11; 24,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12,61; 19,39</t>
+          <t>12,55; 19,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,11; 17,84</t>
+          <t>11,37; 18,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,37; 18,35</t>
+          <t>11,44; 18,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,79; 13,96</t>
+          <t>9,99; 13,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,55; 18,48</t>
+          <t>13,52; 18,2</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,76; 19,8</t>
+          <t>14,97; 20,29</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,27; 14,69</t>
+          <t>9,35; 14,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,01; 17,23</t>
+          <t>11,83; 17,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,19; 20,45</t>
+          <t>14,12; 20,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,29; 14,58</t>
+          <t>9,02; 14,35</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,5; 18,67</t>
+          <t>12,54; 18,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,4; 19,24</t>
+          <t>13,38; 19,29</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,99; 13,69</t>
+          <t>9,93; 13,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>13,05; 17,07</t>
+          <t>12,89; 17,04</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14,58; 18,81</t>
+          <t>14,56; 19,06</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,76; 10,13</t>
+          <t>5,71; 9,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,44; 13,47</t>
+          <t>8,61; 13,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,19; 11,79</t>
+          <t>7,24; 11,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,29; 12,93</t>
+          <t>8,13; 13,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,63; 13,18</t>
+          <t>8,56; 13,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,73; 18,57</t>
+          <t>12,79; 18,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,59; 11,1</t>
+          <t>7,6; 10,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,11; 12,5</t>
+          <t>9,18; 12,65</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10,65; 14,41</t>
+          <t>10,85; 14,39</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,79; 8,05</t>
+          <t>3,89; 8,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,41; 11,59</t>
+          <t>6,5; 11,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,78; 13,91</t>
+          <t>8,87; 14,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,87; 11,99</t>
+          <t>6,89; 12,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,53; 12,8</t>
+          <t>7,41; 12,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,91; 15,34</t>
+          <t>10,22; 15,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,09; 9,37</t>
+          <t>6,04; 9,18</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,65; 11,31</t>
+          <t>7,75; 11,24</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,15; 13,78</t>
+          <t>10,21; 13,96</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,56; 8,5</t>
+          <t>3,82; 8,61</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,21; 14,75</t>
+          <t>8,03; 14,65</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,76; 17,61</t>
+          <t>10,94; 18,08</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,6; 12,18</t>
+          <t>6,54; 12,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,84; 16,74</t>
+          <t>9,63; 16,41</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,03; 15,04</t>
+          <t>8,91; 14,98</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,81; 9,44</t>
+          <t>5,85; 9,36</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,75; 14,51</t>
+          <t>9,86; 14,56</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10,6; 15,13</t>
+          <t>10,71; 15,31</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,86; 11,49</t>
+          <t>5,06; 11,31</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,99; 14,29</t>
+          <t>6,73; 14,47</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,87; 11,98</t>
+          <t>5,9; 12,42</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,82; 14,57</t>
+          <t>7,9; 14,42</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9,79; 17,05</t>
+          <t>9,83; 17,36</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,04; 17,3</t>
+          <t>10,39; 17,28</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,26; 12,01</t>
+          <t>7,42; 12,09</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9,41; 14,67</t>
+          <t>9,47; 14,54</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8,84; 13,78</t>
+          <t>8,7; 13,42</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,13; 11,35</t>
+          <t>4,13; 11,54</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,3; 16,03</t>
+          <t>7,09; 15,88</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,24; 14,26</t>
+          <t>7,33; 14,81</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,78; 9,19</t>
+          <t>3,82; 9,67</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>9,57; 16,54</t>
+          <t>9,73; 16,75</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,06; 10,99</t>
+          <t>4,86; 11,23</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,42; 9,02</t>
+          <t>4,57; 9,09</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9,56; 15,43</t>
+          <t>9,71; 15,19</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,32; 11,07</t>
+          <t>6,71; 11,5</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,11; 9,18</t>
+          <t>7,12; 9,12</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10,89; 13,2</t>
+          <t>10,93; 13,17</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11,88; 14,31</t>
+          <t>11,97; 14,21</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9,54; 11,64</t>
+          <t>9,69; 11,89</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>11,57; 13,81</t>
+          <t>11,47; 13,8</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,17; 14,47</t>
+          <t>12,2; 14,48</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,63; 10,11</t>
+          <t>8,66; 10,12</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>11,44; 13,12</t>
+          <t>11,48; 13,15</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>12,34; 13,99</t>
+          <t>12,37; 14,0</t>
         </is>
       </c>
     </row>
@@ -1750,47 +1750,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>29162; 53147</t>
+          <t>29605; 55076</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>64871; 96045</t>
+          <t>63030; 95273</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>65700; 99945</t>
+          <t>67557; 101584</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>58960; 90640</t>
+          <t>58666; 89984</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>47557; 76418</t>
+          <t>48707; 77810</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>44874; 72463</t>
+          <t>45155; 73355</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>94067; 134116</t>
+          <t>96003; 133928</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>119544; 163093</t>
+          <t>119314; 160629</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>120186; 161239</t>
+          <t>121901; 165225</t>
         </is>
       </c>
     </row>
@@ -1913,47 +1913,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>68172; 108069</t>
+          <t>68743; 104120</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>82438; 118208</t>
+          <t>81141; 120620</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>83773; 120765</t>
+          <t>83406; 119957</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>57896; 90870</t>
+          <t>56218; 89457</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>76164; 113730</t>
+          <t>76381; 114376</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>75512; 108406</t>
+          <t>75375; 108690</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>135796; 186021</t>
+          <t>134885; 186523</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>169048; 221152</t>
+          <t>166999; 220647</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>168211; 217089</t>
+          <t>168068; 219978</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>36538; 64331</t>
+          <t>36274; 63135</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>57280; 91498</t>
+          <t>58490; 91232</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>48126; 78853</t>
+          <t>48443; 78808</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>57198; 89200</t>
+          <t>56093; 90093</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>61194; 93403</t>
+          <t>60708; 95121</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>84175; 122835</t>
+          <t>84595; 122760</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>100576; 147080</t>
+          <t>100648; 145128</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>126468; 173503</t>
+          <t>127367; 175554</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>141644; 191733</t>
+          <t>144415; 191463</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>19614; 41629</t>
+          <t>20104; 42314</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>39308; 71106</t>
+          <t>39889; 71123</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>56523; 89578</t>
+          <t>57110; 90396</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>35300; 61579</t>
+          <t>35414; 63231</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>46372; 78860</t>
+          <t>45671; 78847</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>64242; 99422</t>
+          <t>66249; 100398</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>62820; 96561</t>
+          <t>62246; 94601</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>94020; 139109</t>
+          <t>95252; 138192</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>131112; 177986</t>
+          <t>131951; 180390</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>13766; 32857</t>
+          <t>14789; 33295</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>35264; 63361</t>
+          <t>34469; 62916</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>51429; 84158</t>
+          <t>52277; 86396</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>26660; 49199</t>
+          <t>26440; 49183</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>43957; 74793</t>
+          <t>43032; 73333</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>44874; 74715</t>
+          <t>44254; 74435</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>45935; 74640</t>
+          <t>46234; 74031</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>85453; 127163</t>
+          <t>86369; 127553</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>103330; 147464</t>
+          <t>104408; 149246</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>14214; 33630</t>
+          <t>14798; 33086</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>21668; 44264</t>
+          <t>20852; 44832</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>19630; 40056</t>
+          <t>19723; 41526</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>26833; 49949</t>
+          <t>27104; 49447</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>34661; 60360</t>
+          <t>34781; 61456</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>37931; 65338</t>
+          <t>39260; 65294</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>46122; 76331</t>
+          <t>47187; 76818</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>62461; 97359</t>
+          <t>62866; 96538</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>62917; 98137</t>
+          <t>61949; 95559</t>
         </is>
       </c>
     </row>
@@ -2728,47 +2728,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>8666; 23829</t>
+          <t>8676; 24215</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>18158; 39871</t>
+          <t>17649; 39499</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>18465; 36398</t>
+          <t>18717; 37784</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>12612; 30688</t>
+          <t>12741; 32294</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>37229; 64327</t>
+          <t>37850; 65167</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20202; 43839</t>
+          <t>19408; 44819</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24010; 49064</t>
+          <t>24850; 49435</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>60989; 98435</t>
+          <t>61908; 96902</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>41365; 72429</t>
+          <t>43868; 75235</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>232577; 300228</t>
+          <t>232687; 298110</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>372498; 451700</t>
+          <t>373824; 450597</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>402872; 485161</t>
+          <t>405948; 481800</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>321891; 392999</t>
+          <t>327110; 401198</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>411155; 490463</t>
+          <t>407260; 490212</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>431133; 512593</t>
+          <t>432130; 512662</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>573255; 671909</t>
+          <t>575757; 672395</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>797553; 915117</t>
+          <t>800775; 916990</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>855408; 969735</t>
+          <t>857136; 970154</t>
         </is>
       </c>
     </row>
